--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T20:06:34+00:00</t>
+    <t>2025-01-17T09:25:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T09:25:14+00:00</t>
+    <t>2025-01-17T12:03:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:03:37+00:00</t>
+    <t>2025-01-20T07:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T07:38:35+00:00</t>
+    <t>2025-01-20T07:50:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/StructureDefinition-iv-careplan-schulung.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-20T07:50:11+00:00</t>
+    <t>2025-01-21T10:53:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
